--- a/etf_holdings/2026-09-30_active_etf_full_holdings_all.xlsx
+++ b/etf_holdings/2026-09-30_active_etf_full_holdings_all.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.2%2480</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.2%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2480</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.2%4920</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+0.2%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>4920</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.86%1175</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.86%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1175</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.3%4935</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.3%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>4935</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+1.03%3435</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+1.03%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>3435</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-1.38%6800</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-1.38%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>6800</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3%1890</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1890</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0%548</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>548</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+0.65%154.5</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+0.65%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>154.5</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-1.16%5125</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-1.16%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>5125</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+5.51%1340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+5.51%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-1.93%1775</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.93%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>1775</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+6.13%2595</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+6.13%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>2595</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-0.48%2090</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-0.48%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>2090</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:11</t>
+          <t>2026-09-30 23:15:44</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.36%1520</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.36%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>1520</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:13</t>
+          <t>2026-09-30 23:15:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:14</t>
+          <t>2026-09-30 23:15:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:15</t>
+          <t>2026-09-30 23:15:50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:15</t>
+          <t>2026-09-30 23:15:50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:15</t>
+          <t>2026-09-30 23:15:50</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:15</t>
+          <t>2026-09-30 23:15:50</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:15</t>
+          <t>2026-09-30 23:15:50</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:15</t>
+          <t>2026-09-30 23:15:50</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3569,7 +3599,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3630,7 +3660,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3691,7 +3721,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3752,7 +3782,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3813,7 +3843,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3874,7 +3904,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3935,7 +3965,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3996,7 +4026,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4057,7 +4087,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4118,7 +4148,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4179,7 +4209,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4240,7 +4270,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4301,7 +4331,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4362,7 +4392,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4423,7 +4453,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:21</t>
+          <t>2026-09-30 23:15:57</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4484,7 +4514,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4545,7 +4575,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4606,7 +4636,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4667,7 +4697,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4728,7 +4758,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4789,7 +4819,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4850,7 +4880,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4911,7 +4941,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4972,7 +5002,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5033,7 +5063,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5094,7 +5124,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5155,7 +5185,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5216,7 +5246,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5277,7 +5307,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5338,7 +5368,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:22</t>
+          <t>2026-09-30 23:15:58</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5399,7 +5429,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5460,7 +5490,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5521,7 +5551,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5582,7 +5612,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5643,7 +5673,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5704,7 +5734,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5765,7 +5795,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5826,7 +5856,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5887,7 +5917,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5948,7 +5978,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6009,7 +6039,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6070,7 +6100,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6131,7 +6161,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6192,7 +6222,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6253,7 +6283,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:24</t>
+          <t>2026-09-30 23:15:59</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -6314,7 +6344,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:25</t>
+          <t>2026-09-30 23:16:01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -6375,7 +6405,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:25</t>
+          <t>2026-09-30 23:16:01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -6436,7 +6466,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:25</t>
+          <t>2026-09-30 23:16:01</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -6497,7 +6527,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:25</t>
+          <t>2026-09-30 23:16:01</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -6558,7 +6588,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:25</t>
+          <t>2026-09-30 23:16:01</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -6619,7 +6649,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6680,7 +6710,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -6741,7 +6771,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -6802,7 +6832,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -6863,7 +6893,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -6924,7 +6954,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -6985,7 +7015,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7046,7 +7076,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7107,7 +7137,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7168,7 +7198,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -7229,7 +7259,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -7290,7 +7320,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -7351,7 +7381,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -7412,7 +7442,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7473,7 +7503,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:30</t>
+          <t>2026-09-30 23:16:06</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7534,7 +7564,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7595,7 +7625,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7656,7 +7686,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -7717,7 +7747,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7778,7 +7808,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7839,7 +7869,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7900,7 +7930,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7961,7 +7991,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8022,7 +8052,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8083,7 +8113,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8144,7 +8174,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8205,7 +8235,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8266,7 +8296,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -8327,7 +8357,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -8388,7 +8418,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:31</t>
+          <t>2026-09-30 23:16:07</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -8449,7 +8479,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -8510,7 +8540,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -8571,7 +8601,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -8632,7 +8662,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -8693,7 +8723,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -8754,7 +8784,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -8815,7 +8845,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -8876,7 +8906,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -8937,7 +8967,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -8998,7 +9028,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9059,7 +9089,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9120,7 +9150,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9181,7 +9211,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9242,7 +9272,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9303,7 +9333,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:33</t>
+          <t>2026-09-30 23:16:09</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9364,7 +9394,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:34</t>
+          <t>2026-09-30 23:16:10</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -9425,7 +9455,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:34</t>
+          <t>2026-09-30 23:16:10</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -9486,7 +9516,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:34</t>
+          <t>2026-09-30 23:16:10</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -9547,7 +9577,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:34</t>
+          <t>2026-09-30 23:16:10</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -9608,7 +9638,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:34</t>
+          <t>2026-09-30 23:16:10</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -9669,7 +9699,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -9730,7 +9760,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -9791,7 +9821,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -9852,7 +9882,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -9913,7 +9943,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -9974,7 +10004,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -10035,7 +10065,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -10096,7 +10126,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -10157,7 +10187,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -10218,7 +10248,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -10279,7 +10309,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -10340,7 +10370,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -10401,7 +10431,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -10462,7 +10492,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -10523,7 +10553,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:39</t>
+          <t>2026-09-30 23:16:15</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -10584,7 +10614,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -10645,7 +10675,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -10706,7 +10736,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -10767,7 +10797,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -10828,7 +10858,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -10889,7 +10919,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -10950,7 +10980,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -11011,7 +11041,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -11072,7 +11102,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -11133,7 +11163,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -11194,7 +11224,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -11255,7 +11285,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -11316,7 +11346,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -11377,7 +11407,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -11438,7 +11468,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:40</t>
+          <t>2026-09-30 23:16:17</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -11499,7 +11529,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -11560,7 +11590,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -11621,7 +11651,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -11682,7 +11712,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -11743,7 +11773,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11804,7 +11834,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -11865,7 +11895,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -11926,7 +11956,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11987,7 +12017,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -12048,7 +12078,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -12109,7 +12139,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -12170,7 +12200,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -12231,7 +12261,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -12292,7 +12322,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -12353,7 +12383,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:41</t>
+          <t>2026-09-30 23:16:18</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -12414,7 +12444,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -12475,7 +12505,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -12536,7 +12566,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -12597,7 +12627,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -12658,7 +12688,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -12719,7 +12749,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -12780,7 +12810,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -12841,7 +12871,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -12902,7 +12932,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -12963,7 +12993,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -13024,7 +13054,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -13085,7 +13115,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:42</t>
+          <t>2026-09-30 23:16:19</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -13146,7 +13176,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -13207,7 +13237,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -13268,7 +13298,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -13329,7 +13359,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -13390,7 +13420,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -13451,7 +13481,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -13512,7 +13542,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -13573,7 +13603,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -13634,7 +13664,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13695,7 +13725,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -13756,7 +13786,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -13817,7 +13847,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -13878,7 +13908,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -13939,7 +13969,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -14000,7 +14030,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:47</t>
+          <t>2026-09-30 23:16:25</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -14061,7 +14091,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -14122,7 +14152,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -14183,7 +14213,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -14244,7 +14274,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -14305,7 +14335,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14366,7 +14396,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -14427,7 +14457,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14488,7 +14518,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -14549,7 +14579,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14610,7 +14640,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -14671,7 +14701,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -14732,7 +14762,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -14793,7 +14823,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -14854,7 +14884,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -14915,7 +14945,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:49</t>
+          <t>2026-09-30 23:16:26</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -14976,7 +15006,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -15037,7 +15067,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -15098,7 +15128,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -15159,7 +15189,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -15220,7 +15250,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -15281,7 +15311,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -15342,7 +15372,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -15403,7 +15433,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -15464,7 +15494,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -15525,7 +15555,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -15586,7 +15616,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -15647,7 +15677,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -15708,7 +15738,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -15769,7 +15799,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -15830,7 +15860,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:50</t>
+          <t>2026-09-30 23:16:28</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -15891,7 +15921,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:51</t>
+          <t>2026-09-30 23:16:29</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -15952,7 +15982,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:51</t>
+          <t>2026-09-30 23:16:29</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -16013,7 +16043,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:51</t>
+          <t>2026-09-30 23:16:29</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -16074,7 +16104,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:51</t>
+          <t>2026-09-30 23:16:29</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -16135,7 +16165,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026-09-30 23:01:51</t>
+          <t>2026-09-30 23:16:29</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -16196,7 +16226,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -16257,7 +16287,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -16318,7 +16348,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -16379,7 +16409,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -16440,7 +16470,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -16501,7 +16531,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -16562,7 +16592,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -16623,7 +16653,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -16684,7 +16714,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -16745,7 +16775,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -16806,7 +16836,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -16867,7 +16897,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -16928,7 +16958,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -16989,7 +17019,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -17050,7 +17080,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:21</t>
+          <t>2026-09-30 23:16:35</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -17111,7 +17141,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -17172,7 +17202,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -17233,7 +17263,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -17294,7 +17324,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -17355,7 +17385,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -17416,7 +17446,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -17477,7 +17507,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -17538,7 +17568,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -17599,7 +17629,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17660,7 +17690,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17721,7 +17751,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -17782,7 +17812,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -17843,7 +17873,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -17904,7 +17934,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -17965,7 +17995,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:22</t>
+          <t>2026-09-30 23:16:36</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -18026,7 +18056,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -18087,7 +18117,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -18148,7 +18178,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -18209,7 +18239,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -18270,7 +18300,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -18331,7 +18361,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -18392,7 +18422,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -18453,7 +18483,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -18514,7 +18544,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -18575,7 +18605,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -18636,7 +18666,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -18697,7 +18727,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -18758,7 +18788,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -18819,7 +18849,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -18880,7 +18910,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:24</t>
+          <t>2026-09-30 23:16:37</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -18941,7 +18971,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:25</t>
+          <t>2026-09-30 23:16:38</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -19002,7 +19032,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:25</t>
+          <t>2026-09-30 23:16:38</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -19063,7 +19093,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:25</t>
+          <t>2026-09-30 23:16:38</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -19124,7 +19154,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:25</t>
+          <t>2026-09-30 23:16:38</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -19185,7 +19215,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:25</t>
+          <t>2026-09-30 23:16:38</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -19246,7 +19276,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -19307,7 +19337,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -19368,7 +19398,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -19429,7 +19459,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -19490,7 +19520,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -19551,7 +19581,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -19612,7 +19642,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -19673,7 +19703,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -19734,7 +19764,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19795,7 +19825,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -19856,7 +19886,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -19917,7 +19947,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -19978,7 +20008,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -20039,7 +20069,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -20100,7 +20130,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:32</t>
+          <t>2026-09-30 23:16:44</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -20161,7 +20191,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -20222,7 +20252,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -20283,7 +20313,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -20344,7 +20374,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -20405,7 +20435,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -20466,7 +20496,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -20527,7 +20557,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -20588,7 +20618,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -20649,7 +20679,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -20710,7 +20740,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -20771,7 +20801,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -20832,7 +20862,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -20893,7 +20923,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -20954,7 +20984,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -21015,7 +21045,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:34</t>
+          <t>2026-09-30 23:16:45</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -21076,7 +21106,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21137,7 +21167,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21198,7 +21228,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21259,7 +21289,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -21320,7 +21350,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21381,7 +21411,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -21442,7 +21472,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -21503,7 +21533,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21564,7 +21594,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -21625,7 +21655,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -21686,7 +21716,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -21747,7 +21777,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:35</t>
+          <t>2026-09-30 23:16:47</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -21808,7 +21838,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:40</t>
+          <t>2026-09-30 23:16:52</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -21871,7 +21901,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:40</t>
+          <t>2026-09-30 23:16:52</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -21934,7 +21964,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:40</t>
+          <t>2026-09-30 23:16:52</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -21997,7 +22027,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -22060,7 +22090,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -22123,7 +22153,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -22186,7 +22216,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22249,7 +22279,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22312,7 +22342,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:42</t>
+          <t>2026-09-30 23:16:53</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22375,7 +22405,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -22438,7 +22468,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22501,7 +22531,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22564,7 +22594,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22627,7 +22657,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22690,7 +22720,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22753,7 +22783,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:43</t>
+          <t>2026-09-30 23:16:54</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -22816,7 +22846,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:44</t>
+          <t>2026-09-30 23:16:56</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -22879,7 +22909,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:44</t>
+          <t>2026-09-30 23:16:56</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -22942,7 +22972,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -23003,7 +23033,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -23064,7 +23094,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -23125,7 +23155,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -23186,7 +23216,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -23247,7 +23277,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23308,7 +23338,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23369,7 +23399,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -23430,7 +23460,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -23491,7 +23521,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -23552,7 +23582,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23613,7 +23643,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -23674,7 +23704,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -23735,7 +23765,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -23796,7 +23826,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:50</t>
+          <t>2026-09-30 23:17:01</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -23857,7 +23887,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -23918,7 +23948,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -23979,7 +24009,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -24040,7 +24070,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -24101,7 +24131,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -24162,7 +24192,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -24223,7 +24253,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -24284,7 +24314,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -24345,7 +24375,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -24406,7 +24436,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -24467,7 +24497,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -24528,7 +24558,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -24589,7 +24619,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -24650,7 +24680,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24711,7 +24741,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:51</t>
+          <t>2026-09-30 23:17:02</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24772,7 +24802,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -24833,7 +24863,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24894,7 +24924,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -24955,7 +24985,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -25016,7 +25046,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -25077,7 +25107,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -25138,7 +25168,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -25199,7 +25229,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -25260,7 +25290,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -25321,7 +25351,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -25382,7 +25412,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -25443,7 +25473,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -25504,7 +25534,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -25565,7 +25595,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -25626,7 +25656,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026-09-30 23:02:53</t>
+          <t>2026-09-30 23:17:04</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -25687,7 +25717,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25748,7 +25778,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25809,7 +25839,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -25870,7 +25900,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -25931,7 +25961,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -25992,7 +26022,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -26053,7 +26083,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -26114,7 +26144,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -26175,7 +26205,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -26236,7 +26266,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -26297,7 +26327,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -26358,7 +26388,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -26419,7 +26449,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -26480,7 +26510,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -26541,7 +26571,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:22</t>
+          <t>2026-09-30 23:17:09</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -26602,7 +26632,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -26663,7 +26693,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -26724,7 +26754,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -26785,7 +26815,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26846,7 +26876,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26907,7 +26937,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26968,7 +26998,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -27029,7 +27059,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -27090,7 +27120,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -27151,7 +27181,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -27212,7 +27242,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -27273,7 +27303,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -27334,7 +27364,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -27395,7 +27425,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -27456,7 +27486,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:24</t>
+          <t>2026-09-30 23:17:10</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -27517,7 +27547,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -27578,7 +27608,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -27639,7 +27669,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -27700,7 +27730,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -27761,7 +27791,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -27822,7 +27852,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -27883,7 +27913,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -27944,7 +27974,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -28005,7 +28035,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -28066,7 +28096,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -28127,7 +28157,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -28188,7 +28218,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -28249,7 +28279,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -28310,7 +28340,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -28371,7 +28401,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:25</t>
+          <t>2026-09-30 23:17:12</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -28432,7 +28462,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:26</t>
+          <t>2026-09-30 23:17:13</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -28493,7 +28523,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:26</t>
+          <t>2026-09-30 23:17:13</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -28554,7 +28584,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:26</t>
+          <t>2026-09-30 23:17:13</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -28615,7 +28645,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:26</t>
+          <t>2026-09-30 23:17:13</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -28676,7 +28706,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:26</t>
+          <t>2026-09-30 23:17:13</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -28737,7 +28767,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -28798,7 +28828,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -28859,7 +28889,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -28920,7 +28950,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -28981,7 +29011,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -29042,7 +29072,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -29103,7 +29133,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -29164,7 +29194,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -29225,7 +29255,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -29286,7 +29316,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -29347,7 +29377,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -29408,7 +29438,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -29469,7 +29499,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -29530,7 +29560,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -29591,7 +29621,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:32</t>
+          <t>2026-09-30 23:17:18</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -29652,7 +29682,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -29713,7 +29743,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -29774,7 +29804,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -29835,7 +29865,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -29896,7 +29926,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -29957,7 +29987,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -30018,7 +30048,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -30079,7 +30109,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -30140,7 +30170,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -30201,7 +30231,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -30262,7 +30292,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -30323,7 +30353,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -30384,7 +30414,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -30445,7 +30475,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -30506,7 +30536,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:33</t>
+          <t>2026-09-30 23:17:20</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -30567,7 +30597,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -30628,7 +30658,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -30689,7 +30719,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -30750,7 +30780,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -30811,7 +30841,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -30872,7 +30902,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -30933,7 +30963,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -30994,7 +31024,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -31055,7 +31085,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -31116,7 +31146,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -31177,7 +31207,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -31238,7 +31268,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -31299,7 +31329,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -31360,7 +31390,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -31421,7 +31451,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:35</t>
+          <t>2026-09-30 23:17:21</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -31482,7 +31512,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:36</t>
+          <t>2026-09-30 23:17:22</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -31543,7 +31573,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:36</t>
+          <t>2026-09-30 23:17:22</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -31604,7 +31634,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:36</t>
+          <t>2026-09-30 23:17:22</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -31665,7 +31695,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:36</t>
+          <t>2026-09-30 23:17:22</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -31726,7 +31756,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:36</t>
+          <t>2026-09-30 23:17:22</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -31787,7 +31817,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:36</t>
+          <t>2026-09-30 23:17:22</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -31848,7 +31878,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:36</t>
+          <t>2026-09-30 23:17:22</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -31909,7 +31939,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:36</t>
+          <t>2026-09-30 23:17:22</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -31970,7 +32000,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -32031,7 +32061,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -32092,7 +32122,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -32153,7 +32183,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -32214,7 +32244,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -32275,7 +32305,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -32336,7 +32366,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -32397,7 +32427,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -32458,7 +32488,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -32519,7 +32549,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -32580,7 +32610,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -32641,7 +32671,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -32702,7 +32732,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -32763,7 +32793,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -32824,7 +32854,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:41</t>
+          <t>2026-09-30 23:17:28</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -32885,7 +32915,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -32946,7 +32976,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -33007,7 +33037,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -33068,7 +33098,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -33129,7 +33159,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -33190,7 +33220,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -33251,7 +33281,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -33312,7 +33342,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -33373,7 +33403,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -33434,7 +33464,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
@@ -33495,7 +33525,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C542" t="inlineStr">
@@ -33556,7 +33586,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
@@ -33617,7 +33647,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
@@ -33678,7 +33708,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -33739,7 +33769,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:42</t>
+          <t>2026-09-30 23:17:29</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -33800,7 +33830,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
@@ -33861,7 +33891,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
@@ -33922,7 +33952,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
@@ -33983,7 +34013,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
@@ -34044,7 +34074,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C551" t="inlineStr">
@@ -34105,7 +34135,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
@@ -34166,7 +34196,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
@@ -34227,7 +34257,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
@@ -34288,7 +34318,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
@@ -34349,7 +34379,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
@@ -34410,7 +34440,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
@@ -34471,7 +34501,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C558" t="inlineStr">
@@ -34532,7 +34562,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
@@ -34593,7 +34623,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
@@ -34654,7 +34684,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026-09-30 23:03:43</t>
+          <t>2026-09-30 23:17:31</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
